--- a/data/nzd0505/nzd0505.xlsx
+++ b/data/nzd0505/nzd0505.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I340"/>
+  <dimension ref="A1:I341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11586,6 +11586,39 @@
       <c r="I340" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>278.16</v>
+      </c>
+      <c r="C341" t="n">
+        <v>278.02</v>
+      </c>
+      <c r="D341" t="n">
+        <v>343.72</v>
+      </c>
+      <c r="E341" t="n">
+        <v>323.82</v>
+      </c>
+      <c r="F341" t="n">
+        <v>337.72</v>
+      </c>
+      <c r="G341" t="n">
+        <v>348.54</v>
+      </c>
+      <c r="H341" t="n">
+        <v>386.6</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B374"/>
+  <dimension ref="A1:B375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15343,6 +15376,16 @@
       </c>
       <c r="B374" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>-0.61</v>
       </c>
     </row>
   </sheetData>
@@ -15511,28 +15554,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2686413303695389</v>
+        <v>0.2671551237363227</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K2" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000648168176403896</v>
+        <v>0.0006448155821301427</v>
       </c>
       <c r="M2" t="n">
-        <v>66.16016484364962</v>
+        <v>65.95045472902019</v>
       </c>
       <c r="N2" t="n">
-        <v>5317.332080027864</v>
+        <v>5299.916060202663</v>
       </c>
       <c r="O2" t="n">
-        <v>72.92003894697166</v>
+        <v>72.80052238962756</v>
       </c>
       <c r="P2" t="n">
-        <v>273.440627071121</v>
+        <v>273.4582346748251</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15589,28 +15632,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.503630182005419</v>
+        <v>-1.523271134855895</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05021329592070001</v>
+        <v>0.05165798600831828</v>
       </c>
       <c r="M3" t="n">
-        <v>33.66822499877164</v>
+        <v>33.7082461203394</v>
       </c>
       <c r="N3" t="n">
-        <v>2092.930473026361</v>
+        <v>2090.134649359024</v>
       </c>
       <c r="O3" t="n">
-        <v>45.74855705950036</v>
+        <v>45.71799043439052</v>
       </c>
       <c r="P3" t="n">
-        <v>351.5634146271522</v>
+        <v>351.7909479388771</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15667,28 +15710,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6483364158519135</v>
+        <v>0.6444795303165045</v>
       </c>
       <c r="J4" t="n">
+        <v>340</v>
+      </c>
+      <c r="K4" t="n">
         <v>339</v>
       </c>
-      <c r="K4" t="n">
-        <v>338</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1992476072929878</v>
+        <v>0.1979763585873928</v>
       </c>
       <c r="M4" t="n">
-        <v>7.164351159969767</v>
+        <v>7.165161637518857</v>
       </c>
       <c r="N4" t="n">
-        <v>83.77163402136357</v>
+        <v>83.65766902014316</v>
       </c>
       <c r="O4" t="n">
-        <v>9.152684525392731</v>
+        <v>9.146456637416653</v>
       </c>
       <c r="P4" t="n">
-        <v>333.4222865062279</v>
+        <v>333.4665958466338</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15745,28 +15788,28 @@
         <v>0.142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9004783007782449</v>
+        <v>0.8879436628237333</v>
       </c>
       <c r="J5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2565034307514852</v>
+        <v>0.2499786440618644</v>
       </c>
       <c r="M5" t="n">
-        <v>8.533757310627697</v>
+        <v>8.578104469651334</v>
       </c>
       <c r="N5" t="n">
-        <v>116.2600910668834</v>
+        <v>117.3192492146166</v>
       </c>
       <c r="O5" t="n">
-        <v>10.78239727829036</v>
+        <v>10.83140107348152</v>
       </c>
       <c r="P5" t="n">
-        <v>322.0752528195472</v>
+        <v>322.2193698071657</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15823,28 +15866,28 @@
         <v>0.1081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.795363018943171</v>
+        <v>0.7844716090606991</v>
       </c>
       <c r="J6" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K6" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4253582273795462</v>
+        <v>0.4139565542612429</v>
       </c>
       <c r="M6" t="n">
-        <v>4.927786592672376</v>
+        <v>4.970398307474394</v>
       </c>
       <c r="N6" t="n">
-        <v>42.27382142317823</v>
+        <v>43.20731115685822</v>
       </c>
       <c r="O6" t="n">
-        <v>6.501832158951677</v>
+        <v>6.573226845078315</v>
       </c>
       <c r="P6" t="n">
-        <v>335.8585846229778</v>
+        <v>335.9838085974457</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15901,28 +15944,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7642233738549139</v>
+        <v>0.7539562062047253</v>
       </c>
       <c r="J7" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K7" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4636777345476809</v>
+        <v>0.4514347793774434</v>
       </c>
       <c r="M7" t="n">
-        <v>4.448701129640863</v>
+        <v>4.490819960203476</v>
       </c>
       <c r="N7" t="n">
-        <v>33.41554759844544</v>
+        <v>34.25730742236266</v>
       </c>
       <c r="O7" t="n">
-        <v>5.78061827129637</v>
+        <v>5.852974237288479</v>
       </c>
       <c r="P7" t="n">
-        <v>346.4054501969525</v>
+        <v>346.5234969469655</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15979,28 +16022,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7256759420229614</v>
+        <v>0.7349777353518611</v>
       </c>
       <c r="J8" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K8" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2696031892707598</v>
+        <v>0.2735821232556891</v>
       </c>
       <c r="M8" t="n">
-        <v>5.780197963775523</v>
+        <v>5.814948834713052</v>
       </c>
       <c r="N8" t="n">
-        <v>70.56960034085638</v>
+        <v>71.13361883343748</v>
       </c>
       <c r="O8" t="n">
-        <v>8.400571429424096</v>
+        <v>8.43407486529717</v>
       </c>
       <c r="P8" t="n">
-        <v>351.2588703934076</v>
+        <v>351.1519230337092</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16038,7 +16081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I340"/>
+  <dimension ref="A1:I341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31869,6 +31912,53 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-45.80939481511051,170.74314403707922</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-45.80997899842455,170.74277600053006</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-45.810795337448056,170.74322994941375</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-45.811341482280675,170.74276024319022</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-45.81196893043127,170.74262165841492</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-45.812594067834425,170.74254515909718</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-45.813250417755754,170.74293653361042</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0505/nzd0505.xlsx
+++ b/data/nzd0505/nzd0505.xlsx
@@ -11633,7 +11633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B375"/>
+  <dimension ref="A1:B376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15386,6 +15386,16 @@
       </c>
       <c r="B375" t="n">
         <v>-0.61</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0505/nzd0505.xlsx
+++ b/data/nzd0505/nzd0505.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I341"/>
+  <dimension ref="A1:I342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11617,6 +11617,39 @@
         <v>386.6</v>
       </c>
       <c r="I341" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>346.89</v>
+      </c>
+      <c r="C342" t="n">
+        <v>351.36</v>
+      </c>
+      <c r="D342" t="n">
+        <v>339.65</v>
+      </c>
+      <c r="E342" t="n">
+        <v>334.84</v>
+      </c>
+      <c r="F342" t="n">
+        <v>337.81</v>
+      </c>
+      <c r="G342" t="n">
+        <v>341.99</v>
+      </c>
+      <c r="H342" t="n">
+        <v>351.01</v>
+      </c>
+      <c r="I342" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11633,7 +11666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B376"/>
+  <dimension ref="A1:B377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15396,6 +15429,16 @@
       </c>
       <c r="B376" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>0.28</v>
       </c>
     </row>
   </sheetData>
@@ -15564,28 +15607,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2671551237363227</v>
+        <v>0.3099982846969889</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K2" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006448155821301427</v>
+        <v>0.000871042119046761</v>
       </c>
       <c r="M2" t="n">
-        <v>65.95045472902019</v>
+        <v>65.96533230853031</v>
       </c>
       <c r="N2" t="n">
-        <v>5299.916060202663</v>
+        <v>5296.844207431267</v>
       </c>
       <c r="O2" t="n">
-        <v>72.80052238962756</v>
+        <v>72.77942159313487</v>
       </c>
       <c r="P2" t="n">
-        <v>273.4582346748251</v>
+        <v>272.9445437203727</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15642,28 +15685,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.523271134855895</v>
+        <v>-1.499751005471007</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05165798600831828</v>
+        <v>0.05032413091589683</v>
       </c>
       <c r="M3" t="n">
-        <v>33.7082461203394</v>
+        <v>33.68042007130001</v>
       </c>
       <c r="N3" t="n">
-        <v>2090.134649359024</v>
+        <v>2088.649119333122</v>
       </c>
       <c r="O3" t="n">
-        <v>45.71799043439052</v>
+        <v>45.70174087858275</v>
       </c>
       <c r="P3" t="n">
-        <v>351.7909479388771</v>
+        <v>351.5152545008099</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15720,28 +15763,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6444795303165045</v>
+        <v>0.638119658274529</v>
       </c>
       <c r="J4" t="n">
+        <v>341</v>
+      </c>
+      <c r="K4" t="n">
         <v>340</v>
       </c>
-      <c r="K4" t="n">
-        <v>339</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1979763585873928</v>
+        <v>0.1950993364394388</v>
       </c>
       <c r="M4" t="n">
-        <v>7.165161637518857</v>
+        <v>7.179182221283768</v>
       </c>
       <c r="N4" t="n">
-        <v>83.65766902014316</v>
+        <v>83.75961889446052</v>
       </c>
       <c r="O4" t="n">
-        <v>9.146456637416653</v>
+        <v>9.152028130117417</v>
       </c>
       <c r="P4" t="n">
-        <v>333.4665958466338</v>
+        <v>333.5405319556887</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15798,28 +15841,28 @@
         <v>0.142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8879436628237333</v>
+        <v>0.8815649340719021</v>
       </c>
       <c r="J5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2499786440618644</v>
+        <v>0.2478079767732001</v>
       </c>
       <c r="M5" t="n">
-        <v>8.578104469651334</v>
+        <v>8.588157459673168</v>
       </c>
       <c r="N5" t="n">
-        <v>117.3192492146166</v>
+        <v>117.3239877597077</v>
       </c>
       <c r="O5" t="n">
-        <v>10.83140107348152</v>
+        <v>10.83161981236914</v>
       </c>
       <c r="P5" t="n">
-        <v>322.2193698071657</v>
+        <v>322.2935797222601</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15876,28 +15919,28 @@
         <v>0.1081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7844716090606991</v>
+        <v>0.7734092322346242</v>
       </c>
       <c r="J6" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K6" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4139565542612429</v>
+        <v>0.4026801256103311</v>
       </c>
       <c r="M6" t="n">
-        <v>4.970398307474394</v>
+        <v>5.013758305112984</v>
       </c>
       <c r="N6" t="n">
-        <v>43.20731115685822</v>
+        <v>44.12962469854303</v>
       </c>
       <c r="O6" t="n">
-        <v>6.573226845078315</v>
+        <v>6.643013224323961</v>
       </c>
       <c r="P6" t="n">
-        <v>335.9838085974457</v>
+        <v>336.1125079162198</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15954,28 +15997,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7539562062047253</v>
+        <v>0.7396590882704521</v>
       </c>
       <c r="J7" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K7" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4514347793774434</v>
+        <v>0.4310898151377262</v>
       </c>
       <c r="M7" t="n">
-        <v>4.490819960203476</v>
+        <v>4.552891565772251</v>
       </c>
       <c r="N7" t="n">
-        <v>34.25730742236266</v>
+        <v>35.90904890108155</v>
       </c>
       <c r="O7" t="n">
-        <v>5.852974237288479</v>
+        <v>5.992415948603831</v>
       </c>
       <c r="P7" t="n">
-        <v>346.5234969469655</v>
+        <v>346.6898291346593</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16032,28 +16075,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7349777353518611</v>
+        <v>0.7235343608628122</v>
       </c>
       <c r="J8" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K8" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2735821232556891</v>
+        <v>0.2654511493918208</v>
       </c>
       <c r="M8" t="n">
-        <v>5.814948834713052</v>
+        <v>5.850529874580787</v>
       </c>
       <c r="N8" t="n">
-        <v>71.13361883343748</v>
+        <v>72.04753972835269</v>
       </c>
       <c r="O8" t="n">
-        <v>8.43407486529717</v>
+        <v>8.488082217341718</v>
       </c>
       <c r="P8" t="n">
-        <v>351.1519230337092</v>
+        <v>351.2850548664403</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16091,7 +16134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I341"/>
+  <dimension ref="A1:I342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31969,6 +32012,53 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-45.809653038113645,170.74394750167707</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-45.81024158117594,170.74364164236636</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-45.81078340869776,170.74318044168092</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-45.811372919788916,170.74289471039617</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-45.811969181386,170.74262275935195</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-45.81258271071291,170.74246246490338</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-45.81320976241685,170.7424823241942</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0505/nzd0505.xlsx
+++ b/data/nzd0505/nzd0505.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I342"/>
+  <dimension ref="A1:I343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11652,6 +11652,39 @@
       <c r="I342" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>349.93</v>
+      </c>
+      <c r="C343" t="n">
+        <v>352.05</v>
+      </c>
+      <c r="D343" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="E343" t="n">
+        <v>335.08</v>
+      </c>
+      <c r="F343" t="n">
+        <v>337.87</v>
+      </c>
+      <c r="G343" t="n">
+        <v>346.13</v>
+      </c>
+      <c r="H343" t="n">
+        <v>352.39</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15439,6 +15472,16 @@
       </c>
       <c r="B377" t="n">
         <v>0.28</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -15607,28 +15650,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3099982846969889</v>
+        <v>0.3540826669960999</v>
       </c>
       <c r="J2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000871042119046761</v>
+        <v>0.001139774444927744</v>
       </c>
       <c r="M2" t="n">
-        <v>65.96533230853031</v>
+        <v>65.98833227015682</v>
       </c>
       <c r="N2" t="n">
-        <v>5296.844207431267</v>
+        <v>5294.842535824115</v>
       </c>
       <c r="O2" t="n">
-        <v>72.77942159313487</v>
+        <v>72.76566866197352</v>
       </c>
       <c r="P2" t="n">
-        <v>272.9445437203727</v>
+        <v>272.4154570950884</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15685,28 +15728,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.499751005471007</v>
+        <v>-1.47616405725949</v>
       </c>
       <c r="J3" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05032413091589683</v>
+        <v>0.04899211660919556</v>
       </c>
       <c r="M3" t="n">
-        <v>33.68042007130001</v>
+        <v>33.65498771857093</v>
       </c>
       <c r="N3" t="n">
-        <v>2088.649119333122</v>
+        <v>2087.260262049725</v>
       </c>
       <c r="O3" t="n">
-        <v>45.70174087858275</v>
+        <v>45.68654355551233</v>
       </c>
       <c r="P3" t="n">
-        <v>351.5152545008099</v>
+        <v>351.2385141161708</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15763,28 +15806,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.638119658274529</v>
+        <v>0.6322870948506962</v>
       </c>
       <c r="J4" t="n">
+        <v>342</v>
+      </c>
+      <c r="K4" t="n">
         <v>341</v>
       </c>
-      <c r="K4" t="n">
-        <v>340</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1950993364394388</v>
+        <v>0.192573924008035</v>
       </c>
       <c r="M4" t="n">
-        <v>7.179182221283768</v>
+        <v>7.19025117259361</v>
       </c>
       <c r="N4" t="n">
-        <v>83.75961889446052</v>
+        <v>83.80962614849228</v>
       </c>
       <c r="O4" t="n">
-        <v>9.152028130117417</v>
+        <v>9.154759753728783</v>
       </c>
       <c r="P4" t="n">
-        <v>333.5405319556887</v>
+        <v>333.6084031467657</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15841,28 +15884,28 @@
         <v>0.142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8815649340719021</v>
+        <v>0.8754085423065904</v>
       </c>
       <c r="J5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2478079767732001</v>
+        <v>0.2457496312420143</v>
       </c>
       <c r="M5" t="n">
-        <v>8.588157459673168</v>
+        <v>8.596851390701223</v>
       </c>
       <c r="N5" t="n">
-        <v>117.3239877597077</v>
+        <v>117.3091046418149</v>
       </c>
       <c r="O5" t="n">
-        <v>10.83161981236914</v>
+        <v>10.83093276877919</v>
       </c>
       <c r="P5" t="n">
-        <v>322.2935797222601</v>
+        <v>322.365271575727</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15919,28 +15962,28 @@
         <v>0.1081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7734092322346242</v>
+        <v>0.7625369700947758</v>
       </c>
       <c r="J6" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K6" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4026801256103311</v>
+        <v>0.3917705898693207</v>
       </c>
       <c r="M6" t="n">
-        <v>5.013758305112984</v>
+        <v>5.056624625836559</v>
       </c>
       <c r="N6" t="n">
-        <v>44.12962469854303</v>
+        <v>45.02408522194929</v>
       </c>
       <c r="O6" t="n">
-        <v>6.643013224323961</v>
+        <v>6.70999889880388</v>
       </c>
       <c r="P6" t="n">
-        <v>336.1125079162198</v>
+        <v>336.239116594468</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15997,28 +16040,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7396590882704521</v>
+        <v>0.7279633901987046</v>
       </c>
       <c r="J7" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K7" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4310898151377262</v>
+        <v>0.4167609592754407</v>
       </c>
       <c r="M7" t="n">
-        <v>4.552891565772251</v>
+        <v>4.601398501333904</v>
       </c>
       <c r="N7" t="n">
-        <v>35.90904890108155</v>
+        <v>36.98845055519098</v>
       </c>
       <c r="O7" t="n">
-        <v>5.992415948603831</v>
+        <v>6.081813097686493</v>
       </c>
       <c r="P7" t="n">
-        <v>346.6898291346593</v>
+        <v>346.8260268141308</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16075,28 +16118,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7235343608628122</v>
+        <v>0.7130497825902803</v>
       </c>
       <c r="J8" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K8" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2654511493918208</v>
+        <v>0.2583737836865223</v>
       </c>
       <c r="M8" t="n">
-        <v>5.850529874580787</v>
+        <v>5.883122841347137</v>
       </c>
       <c r="N8" t="n">
-        <v>72.04753972835269</v>
+        <v>72.78867861752201</v>
       </c>
       <c r="O8" t="n">
-        <v>8.488082217341718</v>
+        <v>8.531628134038778</v>
       </c>
       <c r="P8" t="n">
-        <v>351.2850548664403</v>
+        <v>351.4071489237763</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16134,7 +16177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I342"/>
+  <dimension ref="A1:I343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32059,6 +32102,53 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-45.80966445946034,170.74398303993465</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-45.810244051585826,170.74364978656834</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-45.81078563618098,170.7431896863665</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-45.81137360445162,170.74289763890332</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-45.81196934868914,170.74262349330994</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-45.812589889114165,170.7425147326797</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-45.81321133885849,170.74249993612202</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0505/nzd0505.xlsx
+++ b/data/nzd0505/nzd0505.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I343"/>
+  <dimension ref="A1:I348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11685,6 +11685,171 @@
       <c r="I343" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>316.15</v>
+      </c>
+      <c r="C344" t="n">
+        <v>348.75</v>
+      </c>
+      <c r="D344" t="n">
+        <v>337.09</v>
+      </c>
+      <c r="E344" t="n">
+        <v>331.27</v>
+      </c>
+      <c r="F344" t="n">
+        <v>333.93</v>
+      </c>
+      <c r="G344" t="n">
+        <v>342.57</v>
+      </c>
+      <c r="H344" t="n">
+        <v>349.64</v>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>280.44</v>
+      </c>
+      <c r="C345" t="n">
+        <v>346.26</v>
+      </c>
+      <c r="D345" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="E345" t="n">
+        <v>328.28</v>
+      </c>
+      <c r="F345" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="G345" t="n">
+        <v>343.2</v>
+      </c>
+      <c r="H345" t="n">
+        <v>348.29</v>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>262.89</v>
+      </c>
+      <c r="C346" t="n">
+        <v>346.26</v>
+      </c>
+      <c r="D346" t="n">
+        <v>335.61</v>
+      </c>
+      <c r="E346" t="n">
+        <v>326.88</v>
+      </c>
+      <c r="F346" t="n">
+        <v>332.83</v>
+      </c>
+      <c r="G346" t="n">
+        <v>340.85</v>
+      </c>
+      <c r="H346" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>248.62</v>
+      </c>
+      <c r="C347" t="n">
+        <v>346.26</v>
+      </c>
+      <c r="D347" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="E347" t="n">
+        <v>326.88</v>
+      </c>
+      <c r="F347" t="n">
+        <v>332.83</v>
+      </c>
+      <c r="G347" t="n">
+        <v>340.85</v>
+      </c>
+      <c r="H347" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>238.81</v>
+      </c>
+      <c r="C348" t="n">
+        <v>331.46</v>
+      </c>
+      <c r="D348" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="E348" t="n">
+        <v>328.4</v>
+      </c>
+      <c r="F348" t="n">
+        <v>334.93</v>
+      </c>
+      <c r="G348" t="n">
+        <v>342.57</v>
+      </c>
+      <c r="H348" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B378"/>
+  <dimension ref="A1:B383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15482,6 +15647,56 @@
       </c>
       <c r="B378" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -15650,28 +15865,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3540826669960999</v>
+        <v>0.3151436802306218</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K2" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001139774444927744</v>
+        <v>0.0009282686997630352</v>
       </c>
       <c r="M2" t="n">
-        <v>65.98833227015682</v>
+        <v>65.33288432884315</v>
       </c>
       <c r="N2" t="n">
-        <v>5294.842535824115</v>
+        <v>5224.293660285259</v>
       </c>
       <c r="O2" t="n">
-        <v>72.76566866197352</v>
+        <v>72.27927545489965</v>
       </c>
       <c r="P2" t="n">
-        <v>272.4154570950884</v>
+        <v>272.8865312415724</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15728,28 +15943,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.47616405725949</v>
+        <v>-1.385613850313248</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K3" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04899211660919556</v>
+        <v>0.04431588835871747</v>
       </c>
       <c r="M3" t="n">
-        <v>33.65498771857093</v>
+        <v>33.44873771689181</v>
       </c>
       <c r="N3" t="n">
-        <v>2087.260262049725</v>
+        <v>2071.757036407278</v>
       </c>
       <c r="O3" t="n">
-        <v>45.68654355551233</v>
+        <v>45.51655782687524</v>
       </c>
       <c r="P3" t="n">
-        <v>351.2385141161708</v>
+        <v>350.1704440889372</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15806,28 +16021,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6322870948506962</v>
+        <v>0.5856600377806611</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K4" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="L4" t="n">
-        <v>0.192573924008035</v>
+        <v>0.1671458611799207</v>
       </c>
       <c r="M4" t="n">
-        <v>7.19025117259361</v>
+        <v>7.339141426503657</v>
       </c>
       <c r="N4" t="n">
-        <v>83.80962614849228</v>
+        <v>86.64574372624197</v>
       </c>
       <c r="O4" t="n">
-        <v>9.154759753728783</v>
+        <v>9.308369552517883</v>
       </c>
       <c r="P4" t="n">
-        <v>333.6084031467657</v>
+        <v>334.1541053587239</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15884,28 +16099,28 @@
         <v>0.142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8754085423065904</v>
+        <v>0.8265800423626336</v>
       </c>
       <c r="J5" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2457496312420143</v>
+        <v>0.2238213707000721</v>
       </c>
       <c r="M5" t="n">
-        <v>8.596851390701223</v>
+        <v>8.744520397802058</v>
       </c>
       <c r="N5" t="n">
-        <v>117.3091046418149</v>
+        <v>119.8321802874421</v>
       </c>
       <c r="O5" t="n">
-        <v>10.83093276877919</v>
+        <v>10.94678858329885</v>
       </c>
       <c r="P5" t="n">
-        <v>322.365271575727</v>
+        <v>322.9370528801747</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15962,28 +16177,28 @@
         <v>0.1081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7625369700947758</v>
+        <v>0.69814819842848</v>
       </c>
       <c r="J6" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K6" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3917705898693207</v>
+        <v>0.3230869585413625</v>
       </c>
       <c r="M6" t="n">
-        <v>5.056624625836559</v>
+        <v>5.343981137192245</v>
       </c>
       <c r="N6" t="n">
-        <v>45.02408522194929</v>
+        <v>51.64784408151014</v>
       </c>
       <c r="O6" t="n">
-        <v>6.70999889880388</v>
+        <v>7.186643450284016</v>
       </c>
       <c r="P6" t="n">
-        <v>336.239116594468</v>
+        <v>336.9930495450295</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16040,28 +16255,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7279633901987046</v>
+        <v>0.6598883092240669</v>
       </c>
       <c r="J7" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K7" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4167609592754407</v>
+        <v>0.330626064620419</v>
       </c>
       <c r="M7" t="n">
-        <v>4.601398501333904</v>
+        <v>4.900425826308777</v>
       </c>
       <c r="N7" t="n">
-        <v>36.98845055519098</v>
+        <v>44.58780358003664</v>
       </c>
       <c r="O7" t="n">
-        <v>6.081813097686493</v>
+        <v>6.677409945483102</v>
       </c>
       <c r="P7" t="n">
-        <v>346.8260268141308</v>
+        <v>347.6231401401523</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16118,28 +16333,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7130497825902803</v>
+        <v>0.6486409193159285</v>
       </c>
       <c r="J8" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K8" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2583737836865223</v>
+        <v>0.2121347199604675</v>
       </c>
       <c r="M8" t="n">
-        <v>5.883122841347137</v>
+        <v>6.133230384000113</v>
       </c>
       <c r="N8" t="n">
-        <v>72.78867861752201</v>
+        <v>79.03007484666632</v>
       </c>
       <c r="O8" t="n">
-        <v>8.531628134038778</v>
+        <v>8.889886098632891</v>
       </c>
       <c r="P8" t="n">
-        <v>351.4071489237763</v>
+        <v>352.1613608272427</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16177,7 +16392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I343"/>
+  <dimension ref="A1:I348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32149,6 +32364,241 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-45.80953754665182,170.7435881452633</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-45.810232236576816,170.7436108360438</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-45.81077590559093,170.74314930169308</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-45.81136273542261,170.7428511488613</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-45.81195836243935,170.74257529674344</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-45.812583716384076,170.74246978744125</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-45.81320819739602,170.74246483989015</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-45.809403381304854,170.7431706905188</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-45.81022332160686,170.74358144611375</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-45.81077974507241,170.74316523660767</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-45.81135420564669,170.7428146645632</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-45.81195783264506,170.74257297254402</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-45.81258480875051,170.74247774123268</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-45.81320665521961,170.74244761083247</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-45.80933744399426,170.74296552939006</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-45.81022332160686,170.74358144611375</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-45.810771567853486,170.74313129889157</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-45.81135021176773,170.74279758161825</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-45.811955295208655,170.74256184085272</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-45.81258073404753,170.74244807232984</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-45.81320463325108,170.7424250216251</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-45.80928382974447,170.74279871213105</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-45.81022332160686,170.74358144611375</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-45.81075263418309,170.74305271912965</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-45.81135021176773,170.74279758161825</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-45.811955295208655,170.74256184085272</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-45.81258073404753,170.74244807232984</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-45.81320463325108,170.7424250216251</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-45.80924697215783,170.74268403276184</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-45.810170332877696,170.74340675917784</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-45.81075263418309,170.74305271912965</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-45.81135454797906,170.74281612881575</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-45.81196115082951,170.74258752937266</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-45.812583716384076,170.74246978744125</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-45.81320463325108,170.7424250216251</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0505/nzd0505.xlsx
+++ b/data/nzd0505/nzd0505.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I348"/>
+  <dimension ref="A1:I350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11848,6 +11848,72 @@
         <v>346.52</v>
       </c>
       <c r="I348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>213.97</v>
+      </c>
+      <c r="C349" t="n">
+        <v>293.51</v>
+      </c>
+      <c r="D349" t="n">
+        <v>316.07</v>
+      </c>
+      <c r="E349" t="n">
+        <v>323.78</v>
+      </c>
+      <c r="F349" t="n">
+        <v>333.09</v>
+      </c>
+      <c r="G349" t="n">
+        <v>343.01</v>
+      </c>
+      <c r="H349" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>207.89</v>
+      </c>
+      <c r="C350" t="n">
+        <v>268.13</v>
+      </c>
+      <c r="D350" t="n">
+        <v>316.07</v>
+      </c>
+      <c r="E350" t="n">
+        <v>319.09</v>
+      </c>
+      <c r="F350" t="n">
+        <v>330.73</v>
+      </c>
+      <c r="G350" t="n">
+        <v>341.77</v>
+      </c>
+      <c r="H350" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="I350" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11864,7 +11930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B383"/>
+  <dimension ref="A1:B385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15697,6 +15763,26 @@
       </c>
       <c r="B383" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>
@@ -15865,28 +15951,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3151436802306218</v>
+        <v>0.2284394718801576</v>
       </c>
       <c r="J2" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K2" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0009282686997630352</v>
+        <v>0.0004908436412907058</v>
       </c>
       <c r="M2" t="n">
-        <v>65.33288432884315</v>
+        <v>65.3249790570864</v>
       </c>
       <c r="N2" t="n">
-        <v>5224.293660285259</v>
+        <v>5222.074830997608</v>
       </c>
       <c r="O2" t="n">
-        <v>72.27927545489965</v>
+        <v>72.26392482419985</v>
       </c>
       <c r="P2" t="n">
-        <v>272.8865312415724</v>
+        <v>273.9377933572414</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15943,28 +16029,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.385613850313248</v>
+        <v>-1.421910668929792</v>
       </c>
       <c r="J3" t="n">
+        <v>349</v>
+      </c>
+      <c r="K3" t="n">
         <v>347</v>
       </c>
-      <c r="K3" t="n">
-        <v>345</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04431588835871747</v>
+        <v>0.04691027988831253</v>
       </c>
       <c r="M3" t="n">
-        <v>33.44873771689181</v>
+        <v>33.50881345685971</v>
       </c>
       <c r="N3" t="n">
-        <v>2071.757036407278</v>
+        <v>2066.62401734649</v>
       </c>
       <c r="O3" t="n">
-        <v>45.51655782687524</v>
+        <v>45.4601365742173</v>
       </c>
       <c r="P3" t="n">
-        <v>350.1704440889372</v>
+        <v>350.6006601983499</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16021,28 +16107,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5856600377806611</v>
+        <v>0.5479902600594045</v>
       </c>
       <c r="J4" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K4" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1671458611799207</v>
+        <v>0.1418526326711842</v>
       </c>
       <c r="M4" t="n">
-        <v>7.339141426503657</v>
+        <v>7.503013572484476</v>
       </c>
       <c r="N4" t="n">
-        <v>86.64574372624197</v>
+        <v>92.59633145849739</v>
       </c>
       <c r="O4" t="n">
-        <v>9.308369552517883</v>
+        <v>9.62269876170388</v>
       </c>
       <c r="P4" t="n">
-        <v>334.1541053587239</v>
+        <v>334.5968907533876</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16099,28 +16185,28 @@
         <v>0.142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8265800423626336</v>
+        <v>0.8001924191857707</v>
       </c>
       <c r="J5" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K5" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2238213707000721</v>
+        <v>0.2102151374372496</v>
       </c>
       <c r="M5" t="n">
-        <v>8.744520397802058</v>
+        <v>8.845311428591028</v>
       </c>
       <c r="N5" t="n">
-        <v>119.8321802874421</v>
+        <v>122.3295006070522</v>
       </c>
       <c r="O5" t="n">
-        <v>10.94678858329885</v>
+        <v>11.06026675117071</v>
       </c>
       <c r="P5" t="n">
-        <v>322.9370528801747</v>
+        <v>323.2474501407577</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16177,28 +16263,28 @@
         <v>0.1081</v>
       </c>
       <c r="I6" t="n">
-        <v>0.69814819842848</v>
+        <v>0.6716064633094637</v>
       </c>
       <c r="J6" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K6" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3230869585413625</v>
+        <v>0.2960085140120258</v>
       </c>
       <c r="M6" t="n">
-        <v>5.343981137192245</v>
+        <v>5.473888555504208</v>
       </c>
       <c r="N6" t="n">
-        <v>51.64784408151014</v>
+        <v>54.54946003574159</v>
       </c>
       <c r="O6" t="n">
-        <v>7.186643450284016</v>
+        <v>7.385760626756163</v>
       </c>
       <c r="P6" t="n">
-        <v>336.9930495450295</v>
+        <v>337.3052521227647</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16255,28 +16341,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6598883092240669</v>
+        <v>0.6343213645404142</v>
       </c>
       <c r="J7" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K7" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L7" t="n">
-        <v>0.330626064620419</v>
+        <v>0.3019788865579059</v>
       </c>
       <c r="M7" t="n">
-        <v>4.900425826308777</v>
+        <v>5.014364776687208</v>
       </c>
       <c r="N7" t="n">
-        <v>44.58780358003664</v>
+        <v>47.2942318216949</v>
       </c>
       <c r="O7" t="n">
-        <v>6.677409945483102</v>
+        <v>6.877080181421102</v>
       </c>
       <c r="P7" t="n">
-        <v>347.6231401401523</v>
+        <v>347.9238732728024</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16333,28 +16419,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6486409193159285</v>
+        <v>0.6210035167372553</v>
       </c>
       <c r="J8" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K8" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2121347199604675</v>
+        <v>0.1929276124154942</v>
       </c>
       <c r="M8" t="n">
-        <v>6.133230384000113</v>
+        <v>6.25284604104773</v>
       </c>
       <c r="N8" t="n">
-        <v>79.03007484666632</v>
+        <v>82.03586022109218</v>
       </c>
       <c r="O8" t="n">
-        <v>8.889886098632891</v>
+        <v>9.057364971176339</v>
       </c>
       <c r="P8" t="n">
-        <v>352.1613608272427</v>
+        <v>352.4864436301465</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16392,7 +16478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I348"/>
+  <dimension ref="A1:I350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32599,6 +32685,100 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-45.809153644187255,170.7423936526663</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-45.81003445855614,170.74295883037817</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-45.810714297734165,170.74289361352658</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-45.81134136816965,170.74275975510628</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-45.8119560201906,170.74256502133585</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-45.81258447930672,170.74247534247016</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-45.8132026341253,170.7424026876648</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-45.809130800516066,170.74232257749628</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-45.809943588287524,170.7426592681749</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-45.810714297734165,170.74289361352658</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-45.81132798863818,170.74270252727786</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-45.81194943958214,170.74253615233837</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-45.812582329251306,170.74245968738913</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-45.8132026341253,170.7424026876648</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
